--- a/data/trans_orig/IQ28_T-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_T-Habitat-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Talla media, en centímetros, recogida tras medición</t>
+          <t>Talla media, en centímetros, recogida tras medición (tasa de respuesta: 93,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>125,7; 133,4</t>
+          <t>125,8; 133,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>130,93; 138,24</t>
+          <t>131,02; 137,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>129,22; 141,41</t>
+          <t>130,11; 141,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>129,07; 137,61</t>
+          <t>128,59; 136,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>129,7; 137,59</t>
+          <t>129,51; 137,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>134,56; 145,82</t>
+          <t>135,46; 146,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>128,53; 134,45</t>
+          <t>128,53; 134,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>131,55; 136,86</t>
+          <t>131,35; 136,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>134,39; 142,47</t>
+          <t>134,43; 142,54</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>125,23; 131,14</t>
+          <t>125,68; 131,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>129,78; 135,75</t>
+          <t>129,81; 135,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>131,97; 141,12</t>
+          <t>131,45; 140,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>125,91; 131,94</t>
+          <t>126,13; 131,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>129,17; 135,32</t>
+          <t>129,17; 135,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>134,65; 144,43</t>
+          <t>135,02; 144,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>126,77; 130,83</t>
+          <t>126,64; 130,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>130,47; 134,66</t>
+          <t>130,52; 134,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>134,56; 141,35</t>
+          <t>134,95; 141,77</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>124,71; 131,83</t>
+          <t>124,48; 132,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>126,95; 133,51</t>
+          <t>127,18; 133,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>136,5; 156,46</t>
+          <t>136,21; 155,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>124,22; 131,69</t>
+          <t>123,95; 131,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>127,57; 134,51</t>
+          <t>127,62; 134,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>135,29; 145,64</t>
+          <t>135,4; 145,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>125,61; 130,66</t>
+          <t>125,51; 130,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>128,25; 133,09</t>
+          <t>128,47; 133,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>137,88; 152,28</t>
+          <t>138,24; 151,57</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>127,19; 133,95</t>
+          <t>126,87; 133,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>127,4; 133,91</t>
+          <t>127,4; 134,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>127,67; 139,7</t>
+          <t>127,18; 139,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>128,2; 135,1</t>
+          <t>127,98; 134,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>128,37; 134,79</t>
+          <t>128,39; 135,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>136,46; 147,6</t>
+          <t>136,12; 146,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>128,49; 133,15</t>
+          <t>128,37; 133,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>129,17; 133,82</t>
+          <t>129,26; 133,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>133,58; 141,76</t>
+          <t>133,69; 141,91</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>127,5; 130,83</t>
+          <t>127,54; 130,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>130,51; 133,66</t>
+          <t>130,44; 133,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>134,98; 145,4</t>
+          <t>135,0; 144,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128,32; 131,92</t>
+          <t>128,44; 131,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>130,54; 133,79</t>
+          <t>130,52; 133,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>137,77; 142,73</t>
+          <t>137,86; 143,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>128,44; 130,85</t>
+          <t>128,6; 130,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>130,92; 133,24</t>
+          <t>130,94; 133,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>137,38; 142,78</t>
+          <t>137,28; 142,7</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ28_T-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_T-Habitat-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Talla media, en centímetros, recogida tras medición (tasa de respuesta: 93,78%)</t>
+          <t>Talla media, en centímetros, recogida por medición (tasa de respuesta: 93,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>125,8; 133,64</t>
+          <t>126,17; 133,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>131,02; 137,97</t>
+          <t>131,01; 138,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>130,11; 141,02</t>
+          <t>129,48; 141,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>128,59; 136,91</t>
+          <t>128,79; 136,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>129,51; 137,18</t>
+          <t>129,9; 137,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>135,46; 146,36</t>
+          <t>134,58; 145,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>128,53; 134,17</t>
+          <t>128,76; 134,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>131,35; 136,65</t>
+          <t>131,49; 136,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>134,43; 142,54</t>
+          <t>134,86; 142,91</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>125,68; 131,27</t>
+          <t>125,64; 131,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>129,81; 135,71</t>
+          <t>130,05; 135,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>131,45; 140,94</t>
+          <t>131,14; 140,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>126,13; 131,98</t>
+          <t>126,13; 131,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>129,17; 135,21</t>
+          <t>129,33; 135,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>135,02; 144,31</t>
+          <t>135,1; 144,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>126,64; 130,98</t>
+          <t>126,57; 130,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>130,52; 134,77</t>
+          <t>130,48; 134,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>134,95; 141,77</t>
+          <t>134,88; 141,57</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>124,48; 132,14</t>
+          <t>124,69; 132,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>127,18; 133,95</t>
+          <t>127,05; 133,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>136,21; 155,44</t>
+          <t>136,09; 155,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>123,95; 131,4</t>
+          <t>124,49; 131,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>127,62; 134,43</t>
+          <t>127,7; 134,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>135,4; 145,08</t>
+          <t>135,48; 145,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>125,51; 130,59</t>
+          <t>125,5; 130,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>128,47; 133,33</t>
+          <t>128,43; 133,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>138,24; 151,57</t>
+          <t>138,39; 152,12</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>126,87; 133,9</t>
+          <t>126,98; 133,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>127,4; 134,19</t>
+          <t>127,7; 133,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>127,18; 139,64</t>
+          <t>127,33; 139,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>127,98; 134,95</t>
+          <t>128,39; 134,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>128,39; 135,46</t>
+          <t>128,49; 135,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>136,12; 146,34</t>
+          <t>136,3; 146,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>128,37; 133,21</t>
+          <t>128,47; 133,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>129,26; 133,97</t>
+          <t>129,14; 133,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>133,69; 141,91</t>
+          <t>133,73; 141,52</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>127,54; 130,88</t>
+          <t>127,44; 130,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>130,44; 133,69</t>
+          <t>130,37; 133,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>135,0; 144,97</t>
+          <t>135,33; 146,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128,44; 131,98</t>
+          <t>128,56; 131,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>130,52; 133,84</t>
+          <t>130,42; 133,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>137,86; 143,05</t>
+          <t>137,61; 142,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>128,6; 130,91</t>
+          <t>128,65; 130,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>130,94; 133,26</t>
+          <t>130,96; 133,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>137,28; 142,7</t>
+          <t>137,22; 142,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ28_T-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_T-Habitat-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>133,1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>133,5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>142,5</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>129,72</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>134,6</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>135,61</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>133,1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>133,5</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>140,52</t>
+          <t>136,37</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>138,5</t>
+          <t>139,89</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>126,17; 133,88</t>
+          <t>129,07; 137,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>131,01; 138,32</t>
+          <t>129,7; 137,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>129,48; 141,49</t>
+          <t>136,66; 147,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>128,79; 136,94</t>
+          <t>125,7; 133,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>129,9; 137,4</t>
+          <t>130,93; 138,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>134,58; 145,17</t>
+          <t>130,48; 142,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>128,76; 134,33</t>
+          <t>128,53; 134,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>131,49; 136,76</t>
+          <t>131,55; 136,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>134,86; 142,91</t>
+          <t>135,89; 143,81</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>128,93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>132,35</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>140,38</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>128,5</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>132,77</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>136,2</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>128,93</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>132,35</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>139,1</t>
+          <t>137,68</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>137,99</t>
+          <t>139,31</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>125,64; 131,25</t>
+          <t>125,91; 131,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>130,05; 135,7</t>
+          <t>129,17; 135,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>131,14; 140,69</t>
+          <t>136,01; 145,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>126,13; 131,91</t>
+          <t>125,23; 131,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>129,33; 135,43</t>
+          <t>129,78; 135,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>135,1; 144,83</t>
+          <t>133,36; 142,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>126,57; 130,8</t>
+          <t>126,77; 130,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>130,48; 134,61</t>
+          <t>130,47; 134,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>134,88; 141,57</t>
+          <t>136,13; 142,54</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>127,83</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>131,06</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>141,99</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>128,32</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>130,55</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>145,84</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>127,83</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>131,06</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>140,56</t>
+          <t>139,13</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>143,31</t>
+          <t>140,7</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>124,69; 132,05</t>
+          <t>124,22; 131,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>127,05; 133,68</t>
+          <t>127,57; 134,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>136,09; 155,82</t>
+          <t>136,97; 146,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>124,49; 131,81</t>
+          <t>124,71; 131,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>127,7; 134,42</t>
+          <t>126,95; 133,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>135,48; 145,55</t>
+          <t>133,51; 145,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>125,5; 130,77</t>
+          <t>125,61; 130,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>128,43; 133,06</t>
+          <t>128,25; 133,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>138,39; 152,12</t>
+          <t>137,0; 144,54</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>131,51</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>131,85</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>142,29</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>130,27</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>130,98</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>134,87</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>131,51</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>131,85</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>141,49</t>
+          <t>137,44</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>138,13</t>
+          <t>139,79</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>126,98; 133,51</t>
+          <t>128,2; 135,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>127,7; 133,87</t>
+          <t>128,37; 134,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>127,33; 139,43</t>
+          <t>137,25; 148,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>128,39; 134,76</t>
+          <t>127,19; 133,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>128,49; 135,36</t>
+          <t>127,4; 133,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>136,3; 146,61</t>
+          <t>133,01; 141,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>128,47; 133,2</t>
+          <t>128,49; 133,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>129,14; 133,78</t>
+          <t>129,17; 133,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>133,73; 141,52</t>
+          <t>136,01; 143,12</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>130,24</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>132,13</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141,6</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>129,2</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>132,08</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>138,73</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>130,24</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>132,13</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>140,26</t>
+          <t>137,72</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>139,56</t>
+          <t>139,87</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>127,44; 130,91</t>
+          <t>128,32; 131,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>130,37; 133,71</t>
+          <t>130,54; 133,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>135,33; 146,78</t>
+          <t>139,17; 143,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128,56; 131,98</t>
+          <t>127,5; 130,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>130,42; 133,75</t>
+          <t>130,51; 133,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>137,61; 142,73</t>
+          <t>135,0; 140,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>128,65; 130,94</t>
+          <t>128,44; 130,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>130,96; 133,38</t>
+          <t>130,92; 133,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>137,22; 142,97</t>
+          <t>138,08; 141,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ28_T-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_T-Habitat-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -622,329 +627,217 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>133,1</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>133,5</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>142,5</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>129,72</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>134,6</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>136,37</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>131,45</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>134,02</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>139,89</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>133.0960047942134</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>133.4976923944393</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>142.5046679569946</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>129.7210276717215</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>134.6024069668726</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>136.3741426542537</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>131.4543214810011</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>134.0168838295469</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>139.8894546889333</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>129,07; 137,61</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>129,7; 137,59</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>136,66; 147,69</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>125,7; 133,4</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>130,93; 138,24</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>130,48; 142,34</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>128,53; 134,45</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>131,55; 136,86</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>135,89; 143,81</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>129.071879287478</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>129.7010303029939</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>136.664184762943</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>125.6976105225176</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>130.9344410499031</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>130.4838031490594</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>128.5343519857369</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>131.5493816390563</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>135.8889361423686</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>137.6080318960784</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>137.5905254509631</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>147.6897753319774</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>133.396869990902</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>138.2444673840375</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>142.3406714554541</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>134.4487693760736</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>136.8588498020758</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>143.8072240323726</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>128,93</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>132,35</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>140,38</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>128,5</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>132,77</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>137,68</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>128,72</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>132,55</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>139,31</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>125,91; 131,94</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>129,17; 135,32</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>136,01; 145,21</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>125,23; 131,14</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>129,78; 135,75</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>133,36; 142,09</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>126,77; 130,83</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>130,47; 134,66</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>136,13; 142,54</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>128.9332126013929</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>132.3503150172506</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>140.377129031269</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>128.4990637170681</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>132.7687220566634</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>137.6844367267768</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>128.7233768088736</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>132.552470339336</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>139.3087030661454</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>127,83</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>131,06</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>141,99</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>128,32</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>130,55</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>139,13</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>128,07</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>130,82</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>140,7</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>125.9144597082296</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>129.1700487918073</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>136.009192573892</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>125.2277926036344</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>129.7849249144396</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>133.3605654527561</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>126.7742606883619</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>130.4704980472014</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>136.125746876888</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>124,22; 131,69</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>127,57; 134,51</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>136,97; 146,99</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>124,71; 131,83</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>126,95; 133,51</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>133,51; 145,42</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>125,61; 130,66</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>128,25; 133,09</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>137,0; 144,54</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>131.9409106731128</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>135.3239378603926</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>145.2063070714158</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>131.1394850428199</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>135.7503729775518</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>142.0904077583388</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>130.832319599284</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>134.6584812836792</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>142.5413630961376</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -952,217 +845,324 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>131,51</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>131,85</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>142,29</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>130,27</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>130,98</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>137,44</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>130,9</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>131,43</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>139,79</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>127.8313927078989</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>131.0597886546287</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>141.9946607073034</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>128.3200639574823</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>130.550881694537</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>139.1306782958057</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>128.0687416884433</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>130.8180263421417</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>140.7036116548105</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>128,2; 135,1</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>128,37; 134,79</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>137,25; 148,15</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>127,19; 133,95</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>127,4; 133,91</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>133,01; 141,51</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>128,49; 133,15</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>129,17; 133,82</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>136,01; 143,12</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>124.2182626246786</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>127.5726575571515</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>136.9672226169774</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>124.7066324700067</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>126.9472258705474</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>133.5143147756229</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>125.6118286416388</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>128.2457148067793</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>136.9959971564755</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>131.6926246710406</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>134.5141241437777</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>146.9930387607064</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>131.8337338080627</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>133.5117139817598</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>145.4249910001265</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>130.6559398775</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>133.0941749700713</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>144.5417826387949</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>131.5107888270817</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>131.8468200568925</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>142.2877884615368</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>130.265993810654</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>130.9772641290977</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>137.4440496151936</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>130.8981801933617</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>131.4295725286374</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>139.7919263430218</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>128.1955472775518</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>128.3719555545135</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>137.2453814824378</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>127.1912823158919</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>127.4036191773362</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>133.0091373315236</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>128.4934997625202</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>129.1690010690963</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>136.013538508955</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>135.0989414061988</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>134.7898720438742</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>148.1473605277723</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>133.9456094135021</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>133.9106986294844</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>141.5066551439776</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>133.1487650308538</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>133.8155554083129</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>143.1162767451366</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>130,24</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>132,13</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>141,6</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>129,2</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>132,08</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>137,72</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>129,73</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>132,11</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>139,87</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>128,32; 131,92</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>130,54; 133,79</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>139,17; 143,97</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>127,5; 130,83</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>130,51; 133,66</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>135,0; 140,09</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>128,44; 130,85</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>130,92; 133,24</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>138,08; 141,53</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>130.2362463963616</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>132.126185039651</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>141.5953066873152</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>129.2002785025321</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>132.082728575989</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>137.7182405143118</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>129.7318211495245</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>132.1054200025506</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>139.8652017151321</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>128.3204913877227</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>130.5365812752016</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>139.1681920408439</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>127.503702981282</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>130.5102806614116</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>134.9993367631664</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>128.4353032755952</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>130.9228089995232</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>138.0774638792128</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>131.9205990730071</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>133.7879126949009</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>143.9689690384212</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>130.8320922549772</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>133.6635327835879</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>140.0874486762942</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>130.8501360931354</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>133.2420242039933</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>141.5273966735468</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1171,14 +1171,14 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
